--- a/CE国試data/CE_questions_2023.xlsx
+++ b/CE国試data/CE_questions_2023.xlsx
@@ -1202,7 +1202,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
